--- a/procurement-contract-automation/data-model/DATA_MODEL_20260806.xlsx
+++ b/procurement-contract-automation/data-model/DATA_MODEL_20260806.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://people.ey.com/personal/anastasios_kakavoulis_gr_ey_com/Documents/Desktop/Claude Code/Procurement/Vendors' Contracts/LEGAL CONTRACTS/LEGAL CONTRACTS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="366" documentId="8_{2B218882-89EB-4EE6-868B-39937B4B5C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CD5F662-1D98-4F52-9A5B-01BFFD463897}"/>
+  <xr:revisionPtr revIDLastSave="387" documentId="8_{2B218882-89EB-4EE6-868B-39937B4B5C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50D61CBE-5B94-4352-84E4-5456EA3C3B58}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{56EA64E1-D5EC-47F8-8ECF-6CF3DF973406}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="3" xr2:uid="{56EA64E1-D5EC-47F8-8ECF-6CF3DF973406}"/>
   </bookViews>
   <sheets>
     <sheet name="Κοινά Πεδία" sheetId="1" r:id="rId1"/>
@@ -21,8 +21,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'A · Προμήθεια Συστήματος'!$A$1:$K$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'B · Προμήθεια Πλατφόρμας'!$A$1:$N$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'C · Παροχή Υπηρεσιών'!$A$1:$N$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'B · Προμήθεια Πλατφόρμας'!$A$1:$N$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'C · Παροχή Υπηρεσιών'!$A$1:$N$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'D · Πρόσθετη Πράξη'!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Κοινά Πεδία'!$A$1:$K$1</definedName>
   </definedNames>
@@ -2292,7 +2292,7 @@
     <t>Ρήτρες απόκρισης ανά σοβαρότητα (Critical/Major/Minor) ολογράφως</t>
   </si>
   <si>
-    <t>penalties.severity_rates_resοlution[]</t>
+    <t>penalties.severity_rates_resolution[]</t>
   </si>
   <si>
     <t>Ρήτρες αποκατάστασης ανά σοβαρότητα (Critical/Major/Minor)</t>
@@ -6477,6 +6477,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7197D3C9-486C-4568-8EA8-C5C43AEA33E6}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:N69"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -6540,7 +6541,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="54">
         <v>1</v>
       </c>
@@ -6578,7 +6579,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" s="30" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="27">
         <v>2</v>
       </c>
@@ -6618,7 +6619,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" ht="26" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="62">
         <v>3</v>
       </c>
@@ -6658,7 +6659,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="62">
         <v>4</v>
       </c>
@@ -6698,7 +6699,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="54">
         <v>5</v>
       </c>
@@ -6846,7 +6847,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="62">
         <v>8</v>
       </c>
@@ -6886,7 +6887,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" ht="65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="62">
         <v>9</v>
       </c>
@@ -6928,7 +6929,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" ht="65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="62"/>
       <c r="B12" s="63" t="s">
         <v>158</v>
@@ -6960,7 +6961,7 @@
       <c r="M12" s="66"/>
       <c r="N12" s="66"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="62">
         <v>10</v>
       </c>
@@ -7000,7 +7001,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="14" spans="1:14" s="30" customFormat="1" ht="26" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" s="30" customFormat="1" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="27">
         <v>11</v>
       </c>
@@ -7082,7 +7083,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="16" spans="1:14" s="30" customFormat="1" ht="26" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" s="30" customFormat="1" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="71">
         <v>13</v>
       </c>
@@ -7122,7 +7123,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="26" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="62">
         <v>14</v>
       </c>
@@ -7162,7 +7163,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="26" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="62"/>
       <c r="B18" s="63" t="s">
         <v>168</v>
@@ -7192,7 +7193,7 @@
       <c r="M18" s="76"/>
       <c r="N18" s="76"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="62"/>
       <c r="B19" s="63" t="s">
         <v>168</v>
@@ -7226,7 +7227,7 @@
       <c r="M19" s="66"/>
       <c r="N19" s="66"/>
     </row>
-    <row r="20" spans="1:14" ht="26" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="62"/>
       <c r="B20" s="63" t="s">
         <v>168</v>
@@ -7256,7 +7257,7 @@
       <c r="M20" s="66"/>
       <c r="N20" s="66"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="62"/>
       <c r="B21" s="63" t="s">
         <v>168</v>
@@ -7290,7 +7291,7 @@
       <c r="M21" s="66"/>
       <c r="N21" s="66"/>
     </row>
-    <row r="22" spans="1:14" ht="26" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="62"/>
       <c r="B22" s="63" t="s">
         <v>168</v>
@@ -7320,7 +7321,7 @@
       <c r="M22" s="66"/>
       <c r="N22" s="66"/>
     </row>
-    <row r="23" spans="1:14" ht="39" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="54">
         <v>15</v>
       </c>
@@ -7364,7 +7365,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="26" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="54">
         <v>16</v>
       </c>
@@ -7404,7 +7405,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="26" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="54"/>
       <c r="B25" s="55" t="s">
         <v>168</v>
@@ -7442,7 +7443,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="54"/>
       <c r="B26" s="55" t="s">
         <v>168</v>
@@ -7470,7 +7471,7 @@
       <c r="M26" s="58"/>
       <c r="N26" s="58"/>
     </row>
-    <row r="27" spans="1:14" ht="26" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="54"/>
       <c r="B27" s="55" t="s">
         <v>168</v>
@@ -7500,7 +7501,7 @@
       <c r="M27" s="58"/>
       <c r="N27" s="58"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="54"/>
       <c r="B28" s="55" t="s">
         <v>168</v>
@@ -7532,7 +7533,7 @@
       <c r="M28" s="58"/>
       <c r="N28" s="58"/>
     </row>
-    <row r="29" spans="1:14" ht="52" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" ht="52" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="62">
         <v>17</v>
       </c>
@@ -7576,7 +7577,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="26" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="54">
         <v>18</v>
       </c>
@@ -7616,7 +7617,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="26" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="62">
         <v>19</v>
       </c>
@@ -7656,7 +7657,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="54">
         <v>20</v>
       </c>
@@ -7696,7 +7697,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="54"/>
       <c r="B33" s="55" t="s">
         <v>168</v>
@@ -7726,7 +7727,7 @@
       <c r="M33" s="58"/>
       <c r="N33" s="58"/>
     </row>
-    <row r="34" spans="1:14" ht="26" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="54"/>
       <c r="B34" s="55" t="s">
         <v>168</v>
@@ -7756,7 +7757,7 @@
       <c r="M34" s="58"/>
       <c r="N34" s="58"/>
     </row>
-    <row r="35" spans="1:14" ht="26" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="54"/>
       <c r="B35" s="55" t="s">
         <v>168</v>
@@ -7788,7 +7789,7 @@
       <c r="M35" s="58"/>
       <c r="N35" s="58"/>
     </row>
-    <row r="36" spans="1:14" ht="52" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" ht="52" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="54"/>
       <c r="B36" s="55" t="s">
         <v>168</v>
@@ -7820,7 +7821,7 @@
       <c r="M36" s="58"/>
       <c r="N36" s="58"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="54"/>
       <c r="B37" s="55" t="s">
         <v>168</v>
@@ -7850,7 +7851,7 @@
       <c r="M37" s="58"/>
       <c r="N37" s="58"/>
     </row>
-    <row r="38" spans="1:14" ht="26" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="54"/>
       <c r="B38" s="55" t="s">
         <v>168</v>
@@ -7880,7 +7881,7 @@
       <c r="M38" s="58"/>
       <c r="N38" s="58"/>
     </row>
-    <row r="39" spans="1:14" ht="26" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="54"/>
       <c r="B39" s="55" t="s">
         <v>168</v>
@@ -7910,7 +7911,7 @@
       <c r="M39" s="58"/>
       <c r="N39" s="58"/>
     </row>
-    <row r="40" spans="1:14" ht="26" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="54"/>
       <c r="B40" s="55" t="s">
         <v>168</v>
@@ -7940,7 +7941,7 @@
       <c r="M40" s="58"/>
       <c r="N40" s="58"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="54"/>
       <c r="B41" s="55" t="s">
         <v>168</v>
@@ -7970,7 +7971,7 @@
       <c r="M41" s="58"/>
       <c r="N41" s="58"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="54"/>
       <c r="B42" s="55" t="s">
         <v>168</v>
@@ -7998,7 +7999,7 @@
       <c r="M42" s="58"/>
       <c r="N42" s="58"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="54"/>
       <c r="B43" s="55" t="s">
         <v>168</v>
@@ -8026,7 +8027,7 @@
       <c r="M43" s="58"/>
       <c r="N43" s="58"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="54"/>
       <c r="B44" s="55" t="s">
         <v>168</v>
@@ -8054,7 +8055,7 @@
       <c r="M44" s="58"/>
       <c r="N44" s="58"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="54"/>
       <c r="B45" s="55" t="s">
         <v>168</v>
@@ -8082,7 +8083,7 @@
       <c r="M45" s="58"/>
       <c r="N45" s="58"/>
     </row>
-    <row r="46" spans="1:14" s="30" customFormat="1" ht="26" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:14" s="30" customFormat="1" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="27">
         <v>21</v>
       </c>
@@ -8126,7 +8127,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="47" spans="1:14" s="85" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:14" s="85" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="54"/>
       <c r="B47" s="55" t="s">
         <v>204</v>
@@ -8156,7 +8157,7 @@
       <c r="M47" s="66"/>
       <c r="N47" s="66"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="54">
         <v>22</v>
       </c>
@@ -8198,7 +8199,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="26" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:14" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="54"/>
       <c r="B49" s="55" t="s">
         <v>204</v>
@@ -8228,7 +8229,7 @@
       <c r="M49" s="58"/>
       <c r="N49" s="58"/>
     </row>
-    <row r="50" spans="1:14" s="30" customFormat="1" ht="26" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:14" s="30" customFormat="1" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="39">
         <v>23</v>
       </c>
@@ -8268,7 +8269,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="62">
         <v>24</v>
       </c>
@@ -8312,7 +8313,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="26" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:14" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="62"/>
       <c r="B52" s="63" t="s">
         <v>204</v>
@@ -8340,7 +8341,7 @@
       <c r="M52" s="66"/>
       <c r="N52" s="66"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="62"/>
       <c r="B53" s="63" t="s">
         <v>204</v>
@@ -8376,7 +8377,7 @@
       <c r="M53" s="66"/>
       <c r="N53" s="66"/>
     </row>
-    <row r="54" spans="1:14" ht="26" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:14" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="62"/>
       <c r="B54" s="63" t="s">
         <v>204</v>
@@ -8404,7 +8405,7 @@
       <c r="M54" s="66"/>
       <c r="N54" s="66"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="62">
         <v>25</v>
       </c>
@@ -8446,7 +8447,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="39" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="62">
         <v>26</v>
       </c>
@@ -8490,7 +8491,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="26" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:14" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="54">
         <v>27</v>
       </c>
@@ -8530,7 +8531,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="54"/>
       <c r="B58" s="55" t="s">
         <v>188</v>
@@ -8558,7 +8559,7 @@
       <c r="M58" s="58"/>
       <c r="N58" s="58"/>
     </row>
-    <row r="59" spans="1:14" s="30" customFormat="1" ht="26" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:14" s="30" customFormat="1" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="71">
         <v>28</v>
       </c>
@@ -8602,7 +8603,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="60" spans="1:14" s="30" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:14" s="30" customFormat="1" ht="26" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="71">
         <v>29</v>
       </c>
@@ -8642,7 +8643,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="78" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:14" ht="78" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="54">
         <v>30</v>
       </c>
@@ -8686,7 +8687,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="26" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:14" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="62">
         <v>31</v>
       </c>
@@ -8730,7 +8731,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="26" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:14" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="54">
         <v>32</v>
       </c>
@@ -8772,7 +8773,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="64" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:14" s="30" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="39">
         <v>33</v>
       </c>
@@ -8814,7 +8815,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="65" spans="1:14" s="30" customFormat="1" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:14" s="30" customFormat="1" ht="52" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="43">
         <v>34</v>
       </c>
@@ -8856,7 +8857,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="66" spans="1:14" s="30" customFormat="1" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:14" s="30" customFormat="1" ht="52" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="43"/>
       <c r="B66" s="6" t="s">
         <v>277</v>
@@ -8886,7 +8887,7 @@
       <c r="M66" s="36"/>
       <c r="N66" s="36"/>
     </row>
-    <row r="67" spans="1:14" s="30" customFormat="1" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:14" s="30" customFormat="1" ht="52" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="43"/>
       <c r="B67" s="6" t="s">
         <v>277</v>
@@ -8916,7 +8917,7 @@
       <c r="M67" s="36"/>
       <c r="N67" s="36"/>
     </row>
-    <row r="68" spans="1:14" ht="78" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:14" ht="78" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="89">
         <v>35</v>
       </c>
@@ -8958,7 +8959,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="26" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:14" ht="26" hidden="1" x14ac:dyDescent="0.35">
       <c r="B69" s="6" t="s">
         <v>277</v>
       </c>
@@ -8985,7 +8986,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:N69" xr:uid="{00000000-0009-0000-0000-000002000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="commercials.annual_subscription_fee"/>
+        <filter val="term.subscription_start_basis"/>
+        <filter val="term.subscription_start_date"/>
+        <filter val="term.subscription_years"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -10093,7 +10103,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:N28" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
